--- a/translation/review/000scriptAKYO_0033A.xlsx
+++ b/translation/review/000scriptAKYO_0033A.xlsx
@@ -25,13 +25,13 @@
     <t>Well anyway, listen to the great strategy I thought of!</t>
   </si>
   <si>
-    <t>Bueno, de todos modos, ¡escucha la gran estrategia que pensé!</t>
+    <t>Bueno, de todos modos, ¡escucha la gran＿estrategia que pensé!</t>
   </si>
   <si>
     <t>...And then my sister proudly announced her strategy.</t>
   </si>
   <si>
-    <t>...Y entonces mi hermana anunció orgullosamente su estrategia.</t>
+    <t>...Y entonces mi hermana anunció orgullosamente＿su estrategia.</t>
   </si>
   <si>
     <t>How was it? Isn't it awesome?</t>
@@ -46,7 +46,7 @@
     <t>Sorry, even though I listened to it, I don't really understand.</t>
   </si>
   <si>
-    <t>Lo siento, aunque la escuché, no la entiendo realmente.</t>
+    <t>Lo siento, aunque la escuché, no la entiendo＿realmente.</t>
   </si>
   <si>
     <t>Hah? That's like, impossible.</t>
@@ -61,7 +61,7 @@
     <t>...Hmph. This is not something you could call a strategy to begin with.</t>
   </si>
   <si>
-    <t>...Hmph. Esto no es algo que puedas llamar estrategia para empezar.</t>
+    <t>...Hmph. Esto no es algo que puedas llamar＿estrategia para empezar.</t>
   </si>
   <si>
     <t>In other words...</t>
